--- a/tame_output/ON/bt/strategyON_20240210.xlsx
+++ b/tame_output/ON/bt/strategyON_20240210.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>54.8%</t>
+          <t>55.7%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1865</v>
+        <v>1866</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,7 +628,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-02-08</t>
+          <t>2024-02-09</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -657,7 +657,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>17.9%</t>
+          <t>18.0%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>9.4%</t>
+          <t>12.4%</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>76.5%</t>
+          <t>76.4%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1865</v>
+        <v>1866</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-02-08</t>
+          <t>2024-02-09</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>62.9%</t>
+          <t>62.7%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.8</t>
+          <t>2.7</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>-0.3%</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>30.7%</t>
+          <t>30.5%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1865</v>
+        <v>1866</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,7 +944,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-02-08</t>
+          <t>2024-02-09</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-4.7%</t>
+          <t>-4.8%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>1.0%</t>
+          <t>0.4%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>98.9%</t>
+          <t>98.6%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>3.19</t>
+          <t>3.18</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1865</v>
+        <v>1866</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-02-08</t>
+          <t>2024-02-09</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>94.1%</t>
+          <t>93.8%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>-0.1%</t>
         </is>
       </c>
     </row>
@@ -1237,12 +1237,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>24.0%</t>
+          <t>23.9%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>2.14</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1865</v>
+        <v>1866</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-02-08</t>
+          <t>2024-02-09</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>66.5%</t>
+          <t>66.6%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-155.5%</t>
+          <t>-155.3%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>127.8%</t>
+          <t>127.6%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1405,11 +1405,11 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.7%</t>
+          <t>59.6%</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1865</v>
+        <v>1866</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-02-08</t>
+          <t>2024-02-09</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>121.5%</t>
+          <t>121.2%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>37.1%</t>
+          <t>37.0%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>1.0%</t>
+          <t>0.8%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1868"/>
+  <dimension ref="A1:G1869"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374332052494684</v>
+        <v>3.374439043094121</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44525,6 +44525,29 @@
       </c>
       <c r="G1868" t="n">
         <v>4.469845971706634</v>
+      </c>
+    </row>
+    <row r="1869">
+      <c r="A1869" s="2" t="n">
+        <v>45331</v>
+      </c>
+      <c r="B1869" t="n">
+        <v>3.404848910298174</v>
+      </c>
+      <c r="C1869" t="n">
+        <v>3.113383178893385</v>
+      </c>
+      <c r="D1869" t="n">
+        <v>1.620191433811421</v>
+      </c>
+      <c r="E1869" t="n">
+        <v>3.761103328104206</v>
+      </c>
+      <c r="F1869" t="n">
+        <v>2.258112854780415</v>
+      </c>
+      <c r="G1869" t="n">
+        <v>4.468250891761635</v>
       </c>
     </row>
   </sheetData>
